--- a/4_analisis/salidas/preelectoral/tablas_preelectoral.xlsx
+++ b/4_analisis/salidas/preelectoral/tablas_preelectoral.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -442,10 +442,12 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,20 +492,30 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>anomalia_2027</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>exceso_2027</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>anomalia_media</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>p</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>q</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>patron</t>
         </is>
@@ -528,15 +540,21 @@
         <v>23.6</v>
       </c>
       <c r="F5" t="n">
-        <v>67.947</v>
+        <v>8.359</v>
       </c>
       <c r="G5" t="n">
-        <v>0.164</v>
+        <v>37.8</v>
       </c>
       <c r="H5" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="I5" t="inlineStr">
+        <v>48.084</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>se acentúa</t>
         </is>
@@ -561,15 +579,21 @@
         <v>34.2</v>
       </c>
       <c r="F6" t="n">
-        <v>4.109</v>
+        <v>6.363</v>
       </c>
       <c r="G6" t="n">
-        <v>0.182</v>
+        <v>30.6</v>
       </c>
       <c r="H6" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="I6" t="inlineStr">
+        <v>4.86</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -594,15 +618,21 @@
         <v>-232</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.245</v>
+        <v>5.39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.727</v>
+        <v>551.8</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="I7" t="inlineStr">
+        <v>1.633</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -627,15 +657,21 @@
         <v>-155</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.412</v>
+        <v>4.862</v>
       </c>
       <c r="G8" t="n">
-        <v>0.727</v>
+        <v>372.9</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="I8" t="inlineStr">
+        <v>1.346</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -644,31 +680,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cap. 7 · Transferencias de capital</t>
+          <t>Cap. 1 · Personal</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-18.753</v>
+        <v>2.929</v>
       </c>
       <c r="C9" t="n">
-        <v>67.7</v>
+        <v>11.2</v>
       </c>
       <c r="D9" t="n">
-        <v>13.843</v>
+        <v>-8.019</v>
       </c>
       <c r="E9" t="n">
-        <v>158.2</v>
+        <v>-134.8</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.455</v>
+        <v>5.926</v>
       </c>
       <c r="G9" t="n">
-        <v>0.309</v>
+        <v>110.6</v>
       </c>
       <c r="H9" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="I9" t="inlineStr">
+        <v>0.279</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -677,31 +719,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cap. 1 · Personal</t>
+          <t>Cap. 6 · Inversiones reales</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.929</v>
+        <v>-27.867</v>
       </c>
       <c r="C10" t="n">
-        <v>11.2</v>
+        <v>-29.1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.019</v>
+        <v>11.45</v>
       </c>
       <c r="E10" t="n">
-        <v>-134.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.545</v>
+        <v>-3.88</v>
       </c>
       <c r="G10" t="n">
-        <v>0.836</v>
+        <v>-74.7</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="I10" t="inlineStr">
+        <v>-6.766</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -726,15 +774,21 @@
         <v>244.3</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.676</v>
+        <v>-25.948</v>
       </c>
       <c r="G11" t="n">
-        <v>0.418</v>
+        <v>-547.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="I11" t="inlineStr">
+        <v>-10.434</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -743,31 +797,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cap. 6 · Inversiones reales</t>
+          <t>Cap. 7 · Transferencias de capital</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-27.867</v>
+        <v>-18.753</v>
       </c>
       <c r="C12" t="n">
-        <v>-29.1</v>
+        <v>67.7</v>
       </c>
       <c r="D12" t="n">
-        <v>11.45</v>
+        <v>13.843</v>
       </c>
       <c r="E12" t="n">
-        <v>86.09999999999999</v>
+        <v>158.2</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.208</v>
+        <v>-37.858</v>
       </c>
       <c r="G12" t="n">
-        <v>0.327</v>
+        <v>-472.7</v>
       </c>
       <c r="H12" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="I12" t="inlineStr">
+        <v>-14.256</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -792,15 +852,21 @@
         <v>-12.2</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-64.809</v>
+        <v>-62.243</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1</v>
+        <v>-4.4</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
+        <v>-63.954</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>se contrae</t>
         </is>
@@ -824,7 +890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -832,10 +898,12 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -880,20 +948,30 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>anomalia_2027</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>exceso_2027</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>anomalia_media</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>p</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>q</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>patron</t>
         </is>
@@ -918,15 +996,21 @@
         <v>23.6</v>
       </c>
       <c r="F5" t="n">
-        <v>69.202</v>
+        <v>9.513</v>
       </c>
       <c r="G5" t="n">
-        <v>0.164</v>
+        <v>38.4</v>
       </c>
       <c r="H5" t="n">
-        <v>0.764</v>
-      </c>
-      <c r="I5" t="inlineStr">
+        <v>49.305</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>se acentúa</t>
         </is>
@@ -951,15 +1035,21 @@
         <v>11.2</v>
       </c>
       <c r="F6" t="n">
-        <v>25.679</v>
+        <v>5.747</v>
       </c>
       <c r="G6" t="n">
-        <v>0.018</v>
+        <v>-5.4</v>
       </c>
       <c r="H6" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="I6" t="inlineStr">
+        <v>19.035</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>se acentúa</t>
         </is>
@@ -984,17 +1074,23 @@
         <v>11.5</v>
       </c>
       <c r="F7" t="n">
-        <v>19.913</v>
+        <v>-6.668</v>
       </c>
       <c r="G7" t="n">
-        <v>0.109</v>
+        <v>-10.3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.764</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>se acentúa</t>
+        <v>11.052</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>mixto</t>
         </is>
       </c>
     </row>
@@ -1017,15 +1113,21 @@
         <v>119.2</v>
       </c>
       <c r="F8" t="n">
-        <v>10.423</v>
+        <v>1.456</v>
       </c>
       <c r="G8" t="n">
-        <v>0.164</v>
+        <v>9.9</v>
       </c>
       <c r="H8" t="n">
-        <v>0.764</v>
-      </c>
-      <c r="I8" t="inlineStr">
+        <v>7.434</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -1034,31 +1136,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Acceso a la vivienda y fomento de la edificación (26)</t>
+          <t>Servicios Sociales y Promoción Social (23)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.211</v>
+        <v>4.315</v>
       </c>
       <c r="C9" t="n">
-        <v>20.6</v>
+        <v>56.8</v>
       </c>
       <c r="D9" t="n">
-        <v>-14.703</v>
+        <v>-1.033</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2</v>
+        <v>15.7</v>
       </c>
       <c r="F9" t="n">
-        <v>9.254</v>
+        <v>17.592</v>
       </c>
       <c r="G9" t="n">
-        <v>0.182</v>
+        <v>144.1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.764</v>
-      </c>
-      <c r="I9" t="inlineStr">
+        <v>6.958</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -1067,31 +1175,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Comercio, Turismo y Pymes (43)</t>
+          <t>Seguridad ciudadana e instituciones penitenciarias (13)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.976</v>
+        <v>-1.071</v>
       </c>
       <c r="C10" t="n">
-        <v>19.9</v>
+        <v>-0.8</v>
       </c>
       <c r="D10" t="n">
-        <v>-12.577</v>
+        <v>-0.681</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8</v>
+        <v>3.7</v>
       </c>
       <c r="F10" t="n">
-        <v>2.699</v>
+        <v>14.54</v>
       </c>
       <c r="G10" t="n">
-        <v>0.291</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>0.873</v>
-      </c>
-      <c r="I10" t="inlineStr">
+        <v>4.263</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -1100,31 +1214,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Servicios de carácter general (92)</t>
+          <t>Alta Dirección (91)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-2.839</v>
+        <v>8.484</v>
       </c>
       <c r="C11" t="n">
-        <v>23.1</v>
+        <v>6.2</v>
       </c>
       <c r="D11" t="n">
-        <v>8.119</v>
+        <v>-11.632</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4</v>
+        <v>-9.9</v>
       </c>
       <c r="F11" t="n">
-        <v>2.64</v>
+        <v>12.773</v>
       </c>
       <c r="G11" t="n">
-        <v>0.455</v>
+        <v>17.4</v>
       </c>
       <c r="H11" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I11" t="inlineStr">
+        <v>3.208</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -1133,31 +1253,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Servicios Sociales y Promoción Social (23)</t>
+          <t>Acceso a la vivienda y fomento de la edificación (26)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.315</v>
+        <v>33.211</v>
       </c>
       <c r="C12" t="n">
-        <v>56.8</v>
+        <v>20.6</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.033</v>
+        <v>-14.703</v>
       </c>
       <c r="E12" t="n">
-        <v>15.7</v>
+        <v>1.2</v>
       </c>
       <c r="F12" t="n">
-        <v>1.641</v>
+        <v>-10.228</v>
       </c>
       <c r="G12" t="n">
-        <v>0.255</v>
+        <v>-16.1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.873</v>
-      </c>
-      <c r="I12" t="inlineStr">
+        <v>2.76</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -1166,64 +1292,76 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Seguridad ciudadana e instituciones penitenciarias (13)</t>
+          <t>Justicia (11)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.071</v>
+        <v>1.14</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.681</v>
+        <v>-4.669</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7</v>
+        <v>-12.4</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.876</v>
+        <v>5.56</v>
       </c>
       <c r="G13" t="n">
-        <v>0.527</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>se contrae</t>
+        <v>0.677</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>mixto</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alta Dirección (91)</t>
+          <t>Educación (32)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.484</v>
+        <v>-0.45</v>
       </c>
       <c r="C14" t="n">
-        <v>6.2</v>
+        <v>-62.8</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.632</v>
+        <v>-6.19</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.9</v>
+        <v>-96.2</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.574</v>
+        <v>6.089</v>
       </c>
       <c r="G14" t="n">
-        <v>0.745</v>
+        <v>94.7</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9429999999999999</v>
-      </c>
-      <c r="I14" t="inlineStr">
+        <v>-0.183</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -1248,48 +1386,60 @@
         <v>-61.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.61</v>
+        <v>1.827</v>
       </c>
       <c r="G15" t="n">
-        <v>0.891</v>
+        <v>135.8</v>
       </c>
       <c r="H15" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>se contrae</t>
+        <v>-0.465</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>mixto</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Justicia (11)</t>
+          <t>Cultura y Deportes (33)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.14</v>
+        <v>-10.644</v>
       </c>
       <c r="C16" t="n">
-        <v>-1</v>
+        <v>2.7</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.669</v>
+        <v>4.797</v>
       </c>
       <c r="E16" t="n">
-        <v>-12.4</v>
+        <v>6.6</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.764</v>
+        <v>3.894</v>
       </c>
       <c r="G16" t="n">
-        <v>0.764</v>
+        <v>-1.1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9429999999999999</v>
-      </c>
-      <c r="I16" t="inlineStr">
+        <v>-0.651</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -1314,15 +1464,21 @@
         <v>5.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.852</v>
+        <v>0.713</v>
       </c>
       <c r="G17" t="n">
-        <v>0.382</v>
+        <v>-10.7</v>
       </c>
       <c r="H17" t="n">
-        <v>0.891</v>
-      </c>
-      <c r="I17" t="inlineStr">
+        <v>-0.997</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -1331,31 +1487,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cultura y Deportes (33)</t>
+          <t>Servicios de carácter general (92)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-10.644</v>
+        <v>-2.839</v>
       </c>
       <c r="C18" t="n">
-        <v>2.7</v>
+        <v>23.1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.797</v>
+        <v>8.119</v>
       </c>
       <c r="E18" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.923</v>
+        <v>-15.319</v>
       </c>
       <c r="G18" t="n">
-        <v>0.364</v>
+        <v>-28.4</v>
       </c>
       <c r="H18" t="n">
-        <v>0.891</v>
-      </c>
-      <c r="I18" t="inlineStr">
+        <v>-3.346</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -1364,64 +1526,76 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Educación (32)</t>
+          <t>Administración Financiera y Tributaria (93)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.45</v>
+        <v>5.128</v>
       </c>
       <c r="C19" t="n">
-        <v>-62.8</v>
+        <v>1.1</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.19</v>
+        <v>-12.168</v>
       </c>
       <c r="E19" t="n">
-        <v>-96.2</v>
+        <v>-6.6</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.32</v>
+        <v>-5.124</v>
       </c>
       <c r="G19" t="n">
-        <v>0.855</v>
+        <v>-4.9</v>
       </c>
       <c r="H19" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>se contrae</t>
+        <v>-4.055</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>mixto</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Administración Financiera y Tributaria (93)</t>
+          <t>Subvenciones al transporte (44)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.128</v>
+        <v>-8.994999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1</v>
+        <v>-1.1</v>
       </c>
       <c r="D20" t="n">
-        <v>-12.168</v>
+        <v>-40.464</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.6</v>
+        <v>-40.1</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.52</v>
+        <v>32.685</v>
       </c>
       <c r="G20" t="n">
-        <v>0.764</v>
+        <v>29</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9429999999999999</v>
-      </c>
-      <c r="I20" t="inlineStr">
+        <v>-5.592</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -1446,15 +1620,21 @@
         <v>-0.4</v>
       </c>
       <c r="F21" t="n">
-        <v>-8.669</v>
+        <v>-4.068</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6909999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9429999999999999</v>
-      </c>
-      <c r="I21" t="inlineStr">
+        <v>-7.136</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>se contrae</t>
         </is>
@@ -1463,31 +1643,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Infraestructuras (45)</t>
+          <t>Comercio, Turismo y Pymes (43)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-24.572</v>
+        <v>17.976</v>
       </c>
       <c r="C22" t="n">
-        <v>-20.5</v>
+        <v>19.9</v>
       </c>
       <c r="D22" t="n">
-        <v>3.072</v>
+        <v>-12.577</v>
       </c>
       <c r="E22" t="n">
-        <v>17.2</v>
+        <v>-0.8</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.75</v>
+        <v>-28.381</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5639999999999999</v>
+        <v>-64.2</v>
       </c>
       <c r="H22" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I22" t="inlineStr">
+        <v>-7.661</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -1496,64 +1682,76 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Industria y Energía (42)</t>
+          <t>Infraestructuras (45)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-32.656</v>
+        <v>-24.572</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.5</v>
+        <v>-20.5</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.233</v>
+        <v>3.072</v>
       </c>
       <c r="E23" t="n">
-        <v>3.9</v>
+        <v>17.2</v>
       </c>
       <c r="F23" t="n">
-        <v>-21.445</v>
+        <v>-19.817</v>
       </c>
       <c r="G23" t="n">
-        <v>0.909</v>
+        <v>-113.4</v>
       </c>
       <c r="H23" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>se contrae</t>
+        <v>-13.772</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>mixto</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Subvenciones al transporte (44)</t>
+          <t>Otras actuaciones de carácter económico (49)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-8.994999999999999</v>
+        <v>-53.636</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.1</v>
+        <v>-0.3</v>
       </c>
       <c r="D24" t="n">
-        <v>-40.464</v>
+        <v>-3.532</v>
       </c>
       <c r="E24" t="n">
-        <v>-40.1</v>
+        <v>2.7</v>
       </c>
       <c r="F24" t="n">
-        <v>-24.73</v>
+        <v>-3.706</v>
       </c>
       <c r="G24" t="n">
-        <v>0.945</v>
+        <v>-7.3</v>
       </c>
       <c r="H24" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="I24" t="inlineStr">
+        <v>-20.291</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>se contrae</t>
         </is>
@@ -1562,31 +1760,37 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Otras actuaciones de carácter económico (49)</t>
+          <t>Industria y Energía (42)</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>-53.636</v>
+        <v>-32.656</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-3.532</v>
+        <v>-10.233</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-28.584</v>
+        <v>-122.091</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.509</v>
+        <v>-226.1</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
+        <v>-54.993</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>se contrae</t>
         </is>
@@ -1610,7 +1814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1618,10 +1822,12 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1666,20 +1872,30 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>anomalia_2027</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>exceso_2027</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>anomalia_media</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>p</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>q</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>patron</t>
         </is>
@@ -1704,15 +1920,21 @@
         <v>23.6</v>
       </c>
       <c r="F5" t="n">
-        <v>69.202</v>
+        <v>9.513</v>
       </c>
       <c r="G5" t="n">
-        <v>0.164</v>
+        <v>38.4</v>
       </c>
       <c r="H5" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="I5" t="inlineStr">
+        <v>49.305</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>se acentúa</t>
         </is>
@@ -1721,31 +1943,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TURISMO Y EMPLEO (16)</t>
+          <t>TRANSFERENCIAS A CORPORACIONES LOCALES (20)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.222</v>
+        <v>10.535</v>
       </c>
       <c r="C6" t="n">
-        <v>34.2</v>
+        <v>84</v>
       </c>
       <c r="D6" t="n">
-        <v>6.48</v>
+        <v>12.278</v>
       </c>
       <c r="E6" t="n">
-        <v>19.6</v>
+        <v>43.5</v>
       </c>
       <c r="F6" t="n">
-        <v>17.851</v>
+        <v>1.341</v>
       </c>
       <c r="G6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.051</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.018</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>se acentúa</t>
         </is>
@@ -1754,163 +1982,193 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRANSFERENCIAS A CORPORACIONES LOCALES (20)</t>
+          <t>BIENESTAR SOC,IGUALDAD,JUVENT.,INFANCIA Y FAMILIAS (23)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.535</v>
+        <v>4.441</v>
       </c>
       <c r="C7" t="n">
-        <v>84</v>
+        <v>57.4</v>
       </c>
       <c r="D7" t="n">
-        <v>12.278</v>
+        <v>-1.4</v>
       </c>
       <c r="E7" t="n">
-        <v>43.5</v>
+        <v>14.5</v>
       </c>
       <c r="F7" t="n">
-        <v>11.406</v>
+        <v>17.784</v>
       </c>
       <c r="G7" t="n">
-        <v>0.018</v>
+        <v>144</v>
       </c>
       <c r="H7" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>se acentúa</t>
+        <v>6.942</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>mixto</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UNIVERSIDADES, CIENCIA E INNOVACIÓN Y CULTURA (17)</t>
+          <t>TURISMO Y EMPLEO (16)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.08</v>
+        <v>29.236</v>
       </c>
       <c r="C8" t="n">
-        <v>-10.1</v>
+        <v>34.2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.314</v>
+        <v>6.492</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.2</v>
+        <v>19.6</v>
       </c>
       <c r="F8" t="n">
-        <v>2.197</v>
+        <v>-20.65</v>
       </c>
       <c r="G8" t="n">
-        <v>0.182</v>
+        <v>-67.09999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>se acentúa</t>
+        <v>5.026</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>mixto</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BIENESTAR SOC,IGUALDAD,JUVENT.,INFANCIA Y FAMILIAS (23)</t>
+          <t>UNIVERSIDADES, CIENCIA E INNOVACIÓN Y CULTURA (17)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.453</v>
+        <v>4.077</v>
       </c>
       <c r="C9" t="n">
-        <v>57.6</v>
+        <v>-10.1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.41</v>
+        <v>0.332</v>
       </c>
       <c r="E9" t="n">
-        <v>14.3</v>
+        <v>-5.1</v>
       </c>
       <c r="F9" t="n">
-        <v>1.521</v>
+        <v>2.856</v>
       </c>
       <c r="G9" t="n">
-        <v>0.273</v>
+        <v>-8.4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>mixto</t>
+        <v>2.421</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>se acentúa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SANIDAD (14)</t>
+          <t>AGRICULTURA,GANADERÍA,PESCA Y SOBERNÍA ALIMENTARIA (13)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.665</v>
+        <v>2.775</v>
       </c>
       <c r="C10" t="n">
-        <v>-129.7</v>
+        <v>4.9</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.57</v>
+        <v>-6.289</v>
       </c>
       <c r="E10" t="n">
-        <v>-61.9</v>
+        <v>3.6</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.618</v>
+        <v>2.854</v>
       </c>
       <c r="G10" t="n">
-        <v>0.891</v>
+        <v>-9.1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>se contrae</t>
+        <v>-0.22</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>mixto</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AGRICULTURA,GANADERÍA,PESCA Y SOBERNÍA ALIMENTARIA (13)</t>
+          <t>EDUCAC.,FORMAC.PROFESIONAL,ACTIV. FÍSICA Y DEPORT (18)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.769</v>
+        <v>-0.403</v>
       </c>
       <c r="C11" t="n">
-        <v>4.9</v>
+        <v>-49.4</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.289</v>
+        <v>-6.324</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5</v>
+        <v>-69.59999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.76</v>
+        <v>6.023</v>
       </c>
       <c r="G11" t="n">
-        <v>0.382</v>
+        <v>89.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.873</v>
-      </c>
-      <c r="I11" t="inlineStr">
+        <v>-0.235</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -1919,31 +2177,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CONSEJ. PRESIDENCIA, ADMONES. PÚBL.,JUSTICIA Y SEG (08)</t>
+          <t>SANIDAD (14)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.45</v>
+        <v>-1.665</v>
       </c>
       <c r="C12" t="n">
-        <v>4.7</v>
+        <v>-129.7</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.364</v>
+        <v>-1.57</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.6</v>
+        <v>-61.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.957</v>
+        <v>1.803</v>
       </c>
       <c r="G12" t="n">
-        <v>0.655</v>
+        <v>136.1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I12" t="inlineStr">
+        <v>-0.477</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -1952,33 +2216,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EDUCAC.,FORMAC.PROFESIONAL,ACTIV. FÍSICA Y DEPORT (18)</t>
+          <t>CONSEJ. PRESIDENCIA, ADMONES. PÚBL.,JUSTICIA Y SEG (08)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.402</v>
+        <v>2.438</v>
       </c>
       <c r="C13" t="n">
-        <v>-49.3</v>
+        <v>4.6</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.325</v>
+        <v>-6.362</v>
       </c>
       <c r="E13" t="n">
-        <v>-69.59999999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.363</v>
+        <v>0.305</v>
       </c>
       <c r="G13" t="n">
-        <v>0.855</v>
+        <v>21.9</v>
       </c>
       <c r="H13" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>se contrae</t>
+        <v>-1.206</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>mixto</t>
         </is>
       </c>
     </row>
@@ -1989,27 +2259,33 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12.109</v>
+        <v>12.316</v>
       </c>
       <c r="C14" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="D14" t="n">
-        <v>-32.418</v>
+        <v>-32.454</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.5</v>
+        <v>-15.1</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.154</v>
+        <v>-1.121</v>
       </c>
       <c r="G14" t="n">
-        <v>0.745</v>
+        <v>-2.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I14" t="inlineStr">
+        <v>-7.086</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
@@ -2018,31 +2294,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TRANSICIÓN ECOLÓGICA Y ENERGÍA (12)</t>
+          <t>PRESIDENCIA DEL GOBIERNO (06)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-14.617</v>
+        <v>-16.776</v>
       </c>
       <c r="C15" t="n">
-        <v>1.4</v>
+        <v>-2.4</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.712</v>
+        <v>-6.631</v>
       </c>
       <c r="E15" t="n">
-        <v>19.3</v>
+        <v>-5.3</v>
       </c>
       <c r="F15" t="n">
-        <v>-10.165</v>
+        <v>-1.785</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8179999999999999</v>
+        <v>-7.7</v>
       </c>
       <c r="H15" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I15" t="inlineStr">
+        <v>-8.397</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>se contrae</t>
         </is>
@@ -2051,33 +2333,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PRESIDENCIA DEL GOBIERNO (06)</t>
+          <t>OBRAS PÚBLICAS, VIVIENDA Y MOVILIDAD (11)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-16.833</v>
+        <v>-24.714</v>
       </c>
       <c r="C16" t="n">
-        <v>-2.4</v>
+        <v>-1.1</v>
       </c>
       <c r="D16" t="n">
-        <v>-6.443</v>
+        <v>-8.391999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-5</v>
+        <v>-33.5</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.638</v>
+        <v>7.294</v>
       </c>
       <c r="G16" t="n">
-        <v>0.855</v>
+        <v>0.4</v>
       </c>
       <c r="H16" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>se contrae</t>
+        <v>-8.603999999999999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>mixto</t>
         </is>
       </c>
     </row>
@@ -2088,27 +2376,33 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-12.4</v>
+        <v>-11.529</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.8</v>
+        <v>-1.1</v>
       </c>
       <c r="D17" t="n">
-        <v>-13.955</v>
+        <v>-15.912</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="F17" t="n">
-        <v>-13.178</v>
+        <v>-7.997</v>
       </c>
       <c r="G17" t="n">
-        <v>0.745</v>
+        <v>-15.5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I17" t="inlineStr">
+        <v>-11.813</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>se contrae</t>
         </is>
@@ -2117,31 +2411,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OBRAS PÚBLICAS, VIVIENDA Y MOVILIDAD (11)</t>
+          <t>HACIENDA Y RELACIONES CON LA UNIÓN EUROPEA (10)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-24.694</v>
+        <v>-30.077</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.1</v>
+        <v>-33</v>
       </c>
       <c r="D18" t="n">
-        <v>-8.394</v>
+        <v>-9.875999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-33.5</v>
+        <v>-6.4</v>
       </c>
       <c r="F18" t="n">
-        <v>-16.544</v>
+        <v>-22.085</v>
       </c>
       <c r="G18" t="n">
-        <v>0.655</v>
+        <v>-22.6</v>
       </c>
       <c r="H18" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I18" t="inlineStr">
+        <v>-20.679</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>se contrae</t>
         </is>
@@ -2150,31 +2450,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HACIENDA Y RELACIONES CON LA UNIÓN EUROPEA (10)</t>
+          <t>TRANSICIÓN ECOLÓGICA Y ENERGÍA (12)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-29.663</v>
+        <v>-15.209</v>
       </c>
       <c r="C19" t="n">
-        <v>-32.8</v>
+        <v>0.7</v>
       </c>
       <c r="D19" t="n">
-        <v>-9.863</v>
+        <v>-4.061</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.6</v>
+        <v>20.6</v>
       </c>
       <c r="F19" t="n">
-        <v>-19.763</v>
+        <v>-98.40900000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.982</v>
+        <v>-310.4</v>
       </c>
       <c r="H19" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="I19" t="inlineStr">
+        <v>-39.226</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>se contrae</t>
         </is>
@@ -2187,27 +2493,33 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>-235.95</v>
+        <v>-207.851</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>38</v>
+        <v>38.8</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>65.431</v>
+        <v>63.506</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>80.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-85.259</v>
+        <v>3.903</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.218</v>
+        <v>-4.8</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
+        <v>-46.814</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>mixto</t>
         </is>
